--- a/docs/harness/wirelist/HeavyDC-wirelist.xlsx
+++ b/docs/harness/wirelist/HeavyDC-wirelist.xlsx
@@ -1910,10 +1910,14 @@
       <c r="AB9" s="37" t="inlineStr"/>
       <c r="AC9" s="38" t="inlineStr"/>
       <c r="AD9" s="38" t="inlineStr"/>
-      <c r="AE9" s="38" t="inlineStr"/>
+      <c r="AE9" s="38" t="inlineStr">
+        <is>
+          <t>end t_eng_block: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF9" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_eng_block (Engine block ground stud, lug 1 (Route 1 point 5)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG9" s="38" t="inlineStr"/>
@@ -2116,10 +2120,14 @@
       <c r="AB11" s="37" t="inlineStr"/>
       <c r="AC11" s="38" t="inlineStr"/>
       <c r="AD11" s="38" t="inlineStr"/>
-      <c r="AE11" s="38" t="inlineStr"/>
+      <c r="AE11" s="38" t="inlineStr">
+        <is>
+          <t>end t_starter_b: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF11" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_starter_b (Starter B+ stud, lug 1 (Route 1 point 2)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG11" s="38" t="inlineStr"/>
@@ -2455,10 +2463,14 @@
       <c r="AB14" s="53" t="inlineStr"/>
       <c r="AC14" s="54" t="inlineStr"/>
       <c r="AD14" s="54" t="inlineStr"/>
-      <c r="AE14" s="54" t="inlineStr"/>
+      <c r="AE14" s="54" t="inlineStr">
+        <is>
+          <t>end t_alt_b: end row of the wire list (SoT); end t_starter_b_2: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF14" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_alt_b (Alternator B+ stud, rear RH of engine (Route 1 point 3)) is drawing-only: not named in the SoT; end t_starter_b_2 (Starter B+ stud, lug 2 (Route 1 point 2)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG14" s="54" t="inlineStr"/>
@@ -2556,10 +2568,14 @@
       <c r="AB15" s="37" t="inlineStr"/>
       <c r="AC15" s="38" t="inlineStr"/>
       <c r="AD15" s="38" t="inlineStr"/>
-      <c r="AE15" s="38" t="inlineStr"/>
+      <c r="AE15" s="38" t="inlineStr">
+        <is>
+          <t>end t_starter_b_3: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF15" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_starter_b_3 (Starter B+ stud, lug 3 (Route 1 point 2)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG15" s="38" t="inlineStr"/>
@@ -2667,12 +2683,12 @@
       <c r="AD16" s="54" t="inlineStr"/>
       <c r="AE16" s="54" t="inlineStr">
         <is>
-          <t>fuse-box plan pdb GND (53.5 AWG)</t>
+          <t>end t_trunk_neg: end row of the wire list (SoT); fuse-box plan pdb GND (53.5 AWG)</t>
         </is>
       </c>
       <c r="AF16" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_trunk_neg (Battery negative terminal post, trunk RH rear (Route 1 point 1)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG16" s="54" t="inlineStr">
@@ -2778,10 +2794,14 @@
       <c r="AB17" s="37" t="inlineStr"/>
       <c r="AC17" s="38" t="inlineStr"/>
       <c r="AD17" s="38" t="inlineStr"/>
-      <c r="AE17" s="38" t="inlineStr"/>
+      <c r="AE17" s="38" t="inlineStr">
+        <is>
+          <t>end t_trunk_pos: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF17" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_trunk_pos (Battery positive terminal post, trunk RH rear (Route 1 point 1)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG17" s="38" t="inlineStr"/>

--- a/docs/harness/wirelist/HeavyDC-wirelist.xlsx
+++ b/docs/harness/wirelist/HeavyDC-wirelist.xlsx
@@ -1185,7 +1185,7 @@
       </c>
       <c r="R3" s="31" t="inlineStr">
         <is>
-          <t>+12V FP 40A fuse out (BATT FP 40A)</t>
+          <t>+12V Fuel pump rly feed (BATT FP 40A)</t>
         </is>
       </c>
       <c r="S3" s="32" t="inlineStr"/>

--- a/docs/harness/wirelist/HeavyDC-wirelist.xlsx
+++ b/docs/harness/wirelist/HeavyDC-wirelist.xlsx
@@ -1427,7 +1427,7 @@
       </c>
       <c r="V5" s="34" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W5" s="34" t="inlineStr"/>
